--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/23.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/23.xlsx
@@ -426,13 +426,13 @@
         <v>-5.294090371060603</v>
       </c>
       <c r="E2">
-        <v>-27.85687370709974</v>
+        <v>-29.54249173731586</v>
       </c>
       <c r="F2">
-        <v>-5.655142636151521</v>
+        <v>-5.83505409563074</v>
       </c>
       <c r="G2">
-        <v>-18.88121250285785</v>
+        <v>-20.13371711530753</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.017657748333728</v>
       </c>
       <c r="E3">
-        <v>-28.65300208001823</v>
+        <v>-30.22680529427395</v>
       </c>
       <c r="F3">
-        <v>-5.643050128805454</v>
+        <v>-5.456801658694818</v>
       </c>
       <c r="G3">
-        <v>-18.85089073442702</v>
+        <v>-18.82318409957907</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.804969592258655</v>
       </c>
       <c r="E4">
-        <v>-28.67356588048706</v>
+        <v>-30.9249057903484</v>
       </c>
       <c r="F4">
-        <v>-5.528281481882388</v>
+        <v>-5.523625228711252</v>
       </c>
       <c r="G4">
-        <v>-18.68514310857323</v>
+        <v>-20.48665843112764</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.670306752932348</v>
       </c>
       <c r="E5">
-        <v>-29.33805151400257</v>
+        <v>-30.85989048902027</v>
       </c>
       <c r="F5">
-        <v>-5.490130192779054</v>
+        <v>-5.431979629469931</v>
       </c>
       <c r="G5">
-        <v>-18.70807064421985</v>
+        <v>-19.70105195925759</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.587760958300713</v>
       </c>
       <c r="E6">
-        <v>-29.35634654899356</v>
+        <v>-31.57418933662016</v>
       </c>
       <c r="F6">
-        <v>-5.649114606561349</v>
+        <v>-5.405178630519757</v>
       </c>
       <c r="G6">
-        <v>-18.55890959334905</v>
+        <v>-19.62624338892381</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.526187801798077</v>
       </c>
       <c r="E7">
-        <v>-30.17976350628227</v>
+        <v>-32.60620139212418</v>
       </c>
       <c r="F7">
-        <v>-5.641658471568751</v>
+        <v>-5.566182604030076</v>
       </c>
       <c r="G7">
-        <v>-18.57511390602037</v>
+        <v>-19.09218028363313</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.453528227769574</v>
       </c>
       <c r="E8">
-        <v>-30.53726841529181</v>
+        <v>-32.14708884756754</v>
       </c>
       <c r="F8">
-        <v>-5.252554421656156</v>
+        <v>-5.260409001369501</v>
       </c>
       <c r="G8">
-        <v>-18.06415388172974</v>
+        <v>-19.25566550722168</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.332767781248214</v>
       </c>
       <c r="E9">
-        <v>-30.59155802593277</v>
+        <v>-32.03713070595029</v>
       </c>
       <c r="F9">
-        <v>-5.25502626998611</v>
+        <v>-4.996088560279818</v>
       </c>
       <c r="G9">
-        <v>-18.15706987323932</v>
+        <v>-19.66974090252659</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.137864023428751</v>
       </c>
       <c r="E10">
-        <v>-32.09763111869277</v>
+        <v>-33.04856990403747</v>
       </c>
       <c r="F10">
-        <v>-5.244539138666668</v>
+        <v>-5.162553131709393</v>
       </c>
       <c r="G10">
-        <v>-18.13167978081233</v>
+        <v>-19.96340859148611</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.845606563722604</v>
       </c>
       <c r="E11">
-        <v>-32.33684322967395</v>
+        <v>-33.97271370867879</v>
       </c>
       <c r="F11">
-        <v>-5.21464501583444</v>
+        <v>-4.944260925356263</v>
       </c>
       <c r="G11">
-        <v>-17.66125268644553</v>
+        <v>-19.26010992182395</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.452744140312876</v>
       </c>
       <c r="E12">
-        <v>-32.45418051968669</v>
+        <v>-33.9231812599829</v>
       </c>
       <c r="F12">
-        <v>-5.156989816232191</v>
+        <v>-5.111552207453832</v>
       </c>
       <c r="G12">
-        <v>-17.35437479948768</v>
+        <v>-19.11901083232471</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.962797839176698</v>
       </c>
       <c r="E13">
-        <v>-32.99695662153505</v>
+        <v>-34.71134631135889</v>
       </c>
       <c r="F13">
-        <v>-5.150433288239032</v>
+        <v>-4.992062694702212</v>
       </c>
       <c r="G13">
-        <v>-16.95680394862678</v>
+        <v>-18.88419841447694</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.401902717334861</v>
       </c>
       <c r="E14">
-        <v>-33.77297404138547</v>
+        <v>-35.46073856828122</v>
       </c>
       <c r="F14">
-        <v>-5.011517731524362</v>
+        <v>-4.766420384384044</v>
       </c>
       <c r="G14">
-        <v>-16.74801325835619</v>
+        <v>-17.53606752150959</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.800062276419161</v>
       </c>
       <c r="E15">
-        <v>-34.39237418768062</v>
+        <v>-35.9265419331842</v>
       </c>
       <c r="F15">
-        <v>-4.900151189524593</v>
+        <v>-4.306234127637222</v>
       </c>
       <c r="G15">
-        <v>-15.8870453303196</v>
+        <v>-17.68096134374233</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.202624490625658</v>
       </c>
       <c r="E16">
-        <v>-34.77644765369316</v>
+        <v>-35.87336859138613</v>
       </c>
       <c r="F16">
-        <v>-4.70694111976083</v>
+        <v>-4.627768248503462</v>
       </c>
       <c r="G16">
-        <v>-15.75636575988237</v>
+        <v>-17.63668946185152</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.6471775440088348</v>
       </c>
       <c r="E17">
-        <v>-35.64387458562541</v>
+        <v>-37.39230255032791</v>
       </c>
       <c r="F17">
-        <v>-4.629727337411083</v>
+        <v>-4.212684111736866</v>
       </c>
       <c r="G17">
-        <v>-15.77427138593226</v>
+        <v>-16.97624846758805</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.1733831316395142</v>
       </c>
       <c r="E18">
-        <v>-36.45525033052773</v>
+        <v>-38.93951003673659</v>
       </c>
       <c r="F18">
-        <v>-4.471543126539892</v>
+        <v>-4.300013088442198</v>
       </c>
       <c r="G18">
-        <v>-15.22791190284756</v>
+        <v>-17.34982866701707</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.1972223075173096</v>
       </c>
       <c r="E19">
-        <v>-37.16407425305234</v>
+        <v>-38.30061028136441</v>
       </c>
       <c r="F19">
-        <v>-4.457172608836126</v>
+        <v>-4.088062034557501</v>
       </c>
       <c r="G19">
-        <v>-14.80774327910677</v>
+        <v>-16.71658571825983</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.4459129421297091</v>
       </c>
       <c r="E20">
-        <v>-37.59741978050534</v>
+        <v>-38.31836416371148</v>
       </c>
       <c r="F20">
-        <v>-4.134934375677507</v>
+        <v>-3.924925843352374</v>
       </c>
       <c r="G20">
-        <v>-14.81430736283644</v>
+        <v>-16.28117089854308</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5719388955268232</v>
       </c>
       <c r="E21">
-        <v>-38.1616857557571</v>
+        <v>-38.83653933051317</v>
       </c>
       <c r="F21">
-        <v>-3.892797613634795</v>
+        <v>-3.683894951792399</v>
       </c>
       <c r="G21">
-        <v>-14.59722994751747</v>
+        <v>-17.23350936273475</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.5758519985479152</v>
       </c>
       <c r="E22">
-        <v>-39.40690063177925</v>
+        <v>-38.74761142218755</v>
       </c>
       <c r="F22">
-        <v>-3.950452813237044</v>
+        <v>-4.08256995867694</v>
       </c>
       <c r="G22">
-        <v>-14.43945569005313</v>
+        <v>-15.89565033385924</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.472542644887874</v>
       </c>
       <c r="E23">
-        <v>-38.67592794288313</v>
+        <v>-40.19687480852132</v>
       </c>
       <c r="F23">
-        <v>-3.976778329298012</v>
+        <v>-2.997340734882558</v>
       </c>
       <c r="G23">
-        <v>-14.52087099999686</v>
+        <v>-16.36596258547147</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.2751043614911146</v>
       </c>
       <c r="E24">
-        <v>-39.70788112822505</v>
+        <v>-39.90866687301415</v>
       </c>
       <c r="F24">
-        <v>-3.819170662139169</v>
+        <v>-3.637075626186171</v>
       </c>
       <c r="G24">
-        <v>-13.83223446887307</v>
+        <v>-15.7202706821177</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.003966748514569682</v>
       </c>
       <c r="E25">
-        <v>-39.64032761721563</v>
+        <v>-41.00686031190327</v>
       </c>
       <c r="F25">
-        <v>-3.700265148406523</v>
+        <v>-3.350390093588304</v>
       </c>
       <c r="G25">
-        <v>-14.01559569205796</v>
+        <v>-15.98818242244636</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.3245907838587347</v>
       </c>
       <c r="E26">
-        <v>-39.48091853943463</v>
+        <v>-41.48047529446949</v>
       </c>
       <c r="F26">
-        <v>-3.53811222930852</v>
+        <v>-3.278520109354016</v>
       </c>
       <c r="G26">
-        <v>-14.24489401707508</v>
+        <v>-15.51926961182924</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.6905403093185625</v>
       </c>
       <c r="E27">
-        <v>-39.61988834978201</v>
+        <v>-41.39615963692067</v>
       </c>
       <c r="F27">
-        <v>-3.625157075994692</v>
+        <v>-3.151571976507589</v>
       </c>
       <c r="G27">
-        <v>-14.47835949347269</v>
+        <v>-16.07038522556435</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.077176648677577</v>
       </c>
       <c r="E28">
-        <v>-39.80542898682428</v>
+        <v>-42.16417750743654</v>
       </c>
       <c r="F28">
-        <v>-3.342573618775488</v>
+        <v>-3.298743871125963</v>
       </c>
       <c r="G28">
-        <v>-14.6845104409987</v>
+        <v>-16.21806316429028</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.467219875884538</v>
       </c>
       <c r="E29">
-        <v>-40.23675707910687</v>
+        <v>-41.04165710617821</v>
       </c>
       <c r="F29">
-        <v>-3.615756762707723</v>
+        <v>-3.131817899053029</v>
       </c>
       <c r="G29">
-        <v>-14.5517013577694</v>
+        <v>-16.71481549922851</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.844944725495816</v>
       </c>
       <c r="E30">
-        <v>-39.90230210279637</v>
+        <v>-41.53815446790518</v>
       </c>
       <c r="F30">
-        <v>-3.686926776486645</v>
+        <v>-3.200772030029463</v>
       </c>
       <c r="G30">
-        <v>-14.24946968053972</v>
+        <v>-16.08441736956332</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.196232128703127</v>
       </c>
       <c r="E31">
-        <v>-39.59677501844686</v>
+        <v>-41.16879854241756</v>
       </c>
       <c r="F31">
-        <v>-3.703055918186554</v>
+        <v>-3.294244179393957</v>
       </c>
       <c r="G31">
-        <v>-14.6373740526865</v>
+        <v>-16.98884507715476</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.507678000350213</v>
       </c>
       <c r="E32">
-        <v>-38.87035118169144</v>
+        <v>-41.3468785185322</v>
       </c>
       <c r="F32">
-        <v>-3.477291837860174</v>
+        <v>-3.330021367520867</v>
       </c>
       <c r="G32">
-        <v>-14.18567124914866</v>
+        <v>-15.77731635953942</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.767493982346013</v>
       </c>
       <c r="E33">
-        <v>-39.17981350995361</v>
+        <v>-41.81195506335695</v>
       </c>
       <c r="F33">
-        <v>-3.508313368727613</v>
+        <v>-3.216408293124707</v>
       </c>
       <c r="G33">
-        <v>-14.77678659430419</v>
+        <v>-16.54276628736981</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.963650013949215</v>
       </c>
       <c r="E34">
-        <v>-38.60629812654118</v>
+        <v>-39.64579348534289</v>
       </c>
       <c r="F34">
-        <v>-3.587438194675619</v>
+        <v>-3.695368668688575</v>
       </c>
       <c r="G34">
-        <v>-14.35215386863177</v>
+        <v>-16.20247736188292</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.086811152845161</v>
       </c>
       <c r="E35">
-        <v>-38.46837212945257</v>
+        <v>-39.07515368292534</v>
       </c>
       <c r="F35">
-        <v>-3.474704846461232</v>
+        <v>-3.257113438930872</v>
       </c>
       <c r="G35">
-        <v>-14.54427923460193</v>
+        <v>-16.86353850702112</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.129554968741902</v>
       </c>
       <c r="E36">
-        <v>-38.16359450755133</v>
+        <v>-39.72097294658123</v>
       </c>
       <c r="F36">
-        <v>-3.414742643642187</v>
+        <v>-3.314940938952902</v>
       </c>
       <c r="G36">
-        <v>-15.0439174039017</v>
+        <v>-16.83726576599465</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.088162841153038</v>
       </c>
       <c r="E37">
-        <v>-37.43304296673792</v>
+        <v>-39.94860122105079</v>
       </c>
       <c r="F37">
-        <v>-3.51062037194441</v>
+        <v>-3.263140640153641</v>
       </c>
       <c r="G37">
-        <v>-14.84143322146837</v>
+        <v>-16.51674948162497</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.963206509785123</v>
       </c>
       <c r="E38">
-        <v>-37.79780022687075</v>
+        <v>-38.88215917766644</v>
       </c>
       <c r="F38">
-        <v>-3.307654619277878</v>
+        <v>-3.44814738752748</v>
       </c>
       <c r="G38">
-        <v>-14.64875989149777</v>
+        <v>-16.73899646151084</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.759409168138217</v>
       </c>
       <c r="E39">
-        <v>-36.77549042692815</v>
+        <v>-37.41698726214372</v>
       </c>
       <c r="F39">
-        <v>-3.556470507689363</v>
+        <v>-3.101545212317721</v>
       </c>
       <c r="G39">
-        <v>-14.67666011841773</v>
+        <v>-16.72672305226774</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.487752193265282</v>
       </c>
       <c r="E40">
-        <v>-36.35581862674131</v>
+        <v>-38.6576668714472</v>
       </c>
       <c r="F40">
-        <v>-3.375264309959568</v>
+        <v>-3.283363573558185</v>
       </c>
       <c r="G40">
-        <v>-15.20776520247257</v>
+        <v>-16.48074627806396</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.162566793386119</v>
       </c>
       <c r="E41">
-        <v>-36.27085313317239</v>
+        <v>-37.77524616207555</v>
       </c>
       <c r="F41">
-        <v>-3.282489645948231</v>
+        <v>-3.196839769968374</v>
       </c>
       <c r="G41">
-        <v>-14.99979481759185</v>
+        <v>-16.45105122295099</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.804584811749634</v>
       </c>
       <c r="E42">
-        <v>-35.86952618119062</v>
+        <v>-36.71814636056902</v>
       </c>
       <c r="F42">
-        <v>-3.256904690345366</v>
+        <v>-3.166981266934465</v>
       </c>
       <c r="G42">
-        <v>-15.30154579586306</v>
+        <v>-16.72090380583206</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.434772412493277</v>
       </c>
       <c r="E43">
-        <v>-35.15394351120957</v>
+        <v>-37.16642453106232</v>
       </c>
       <c r="F43">
-        <v>-3.648717501665115</v>
+        <v>-3.365528507874465</v>
       </c>
       <c r="G43">
-        <v>-14.5706258031135</v>
+        <v>-16.89031491555697</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.077648967631703</v>
       </c>
       <c r="E44">
-        <v>-34.47312140771139</v>
+        <v>-36.9850432973961</v>
       </c>
       <c r="F44">
-        <v>-3.206112514675311</v>
+        <v>-3.415107953666821</v>
       </c>
       <c r="G44">
-        <v>-14.96792267197418</v>
+        <v>-16.49689152874721</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7527154337355815</v>
       </c>
       <c r="E45">
-        <v>-34.41470182877543</v>
+        <v>-36.48220154358438</v>
       </c>
       <c r="F45">
-        <v>-3.614182864642404</v>
+        <v>-3.464097601868384</v>
       </c>
       <c r="G45">
-        <v>-15.45394541241303</v>
+        <v>-16.84903550772838</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.4782617336444684</v>
       </c>
       <c r="E46">
-        <v>-33.29663065322964</v>
+        <v>-35.39984191406307</v>
       </c>
       <c r="F46">
-        <v>-3.285933997609072</v>
+        <v>-3.515033085099123</v>
       </c>
       <c r="G46">
-        <v>-15.03031838114858</v>
+        <v>-16.81826749316546</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.2629613602043024</v>
       </c>
       <c r="E47">
-        <v>-33.34994890619595</v>
+        <v>-35.95695742885672</v>
       </c>
       <c r="F47">
-        <v>-3.280885926656412</v>
+        <v>-3.516047835167552</v>
       </c>
       <c r="G47">
-        <v>-15.50329826588864</v>
+        <v>-16.91238769298736</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.1119588437995218</v>
       </c>
       <c r="E48">
-        <v>-32.7640187112915</v>
+        <v>-35.50768072984473</v>
       </c>
       <c r="F48">
-        <v>-3.46804063070571</v>
+        <v>-3.178257004021372</v>
       </c>
       <c r="G48">
-        <v>-15.61536838825147</v>
+        <v>-15.98929311594423</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.02074984024969117</v>
       </c>
       <c r="E49">
-        <v>-32.2690429168311</v>
+        <v>-34.20030575535629</v>
       </c>
       <c r="F49">
-        <v>-3.373710292711916</v>
+        <v>-3.173978486385913</v>
       </c>
       <c r="G49">
-        <v>-15.52321364014369</v>
+        <v>-16.65487414378057</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.01789271823935997</v>
       </c>
       <c r="E50">
-        <v>-31.37821962393822</v>
+        <v>-33.03686606296465</v>
       </c>
       <c r="F50">
-        <v>-3.204644647637551</v>
+        <v>-3.088525761847922</v>
       </c>
       <c r="G50">
-        <v>-15.20039557885006</v>
+        <v>-16.74125394194374</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.01722581847924397</v>
       </c>
       <c r="E51">
-        <v>-31.50511199410715</v>
+        <v>-33.48589369590621</v>
       </c>
       <c r="F51">
-        <v>-3.403056864690894</v>
+        <v>-3.631210784974351</v>
       </c>
       <c r="G51">
-        <v>-15.66356625173816</v>
+        <v>-17.27354026575998</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.009900623551958731</v>
       </c>
       <c r="E52">
-        <v>-30.76927798836379</v>
+        <v>-32.76164126243747</v>
       </c>
       <c r="F52">
-        <v>-3.177268761709833</v>
+        <v>-3.090412782791499</v>
       </c>
       <c r="G52">
-        <v>-15.8517049335136</v>
+        <v>-16.63657969297589</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.04888333234085299</v>
       </c>
       <c r="E53">
-        <v>-30.56349280827023</v>
+        <v>-33.3473812614336</v>
       </c>
       <c r="F53">
-        <v>-3.304923491950848</v>
+        <v>-3.752714058882177</v>
       </c>
       <c r="G53">
-        <v>-15.63941646106064</v>
+        <v>-16.98627588067371</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.08844834223202069</v>
       </c>
       <c r="E54">
-        <v>-29.88760900567742</v>
+        <v>-32.04458230992991</v>
       </c>
       <c r="F54">
-        <v>-3.363609180602179</v>
+        <v>-3.447776278931025</v>
       </c>
       <c r="G54">
-        <v>-15.800959201486</v>
+        <v>-15.9963346174108</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.119774221211569</v>
       </c>
       <c r="E55">
-        <v>-29.89945096520747</v>
+        <v>-31.8990484765084</v>
       </c>
       <c r="F55">
-        <v>-3.465871964845181</v>
+        <v>-3.550534426880901</v>
       </c>
       <c r="G55">
-        <v>-15.77250608873328</v>
+        <v>-16.77437623297555</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.1384322604859728</v>
       </c>
       <c r="E56">
-        <v>-29.19996022761267</v>
+        <v>-31.57531466241106</v>
       </c>
       <c r="F56">
-        <v>-3.48613797335467</v>
+        <v>-3.544730884856888</v>
       </c>
       <c r="G56">
-        <v>-15.73680639816652</v>
+        <v>-16.77133454058995</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.1438083070133091</v>
       </c>
       <c r="E57">
-        <v>-28.84817930974883</v>
+        <v>-31.95396980927343</v>
       </c>
       <c r="F57">
-        <v>-3.399247203005419</v>
+        <v>-3.14396176517807</v>
       </c>
       <c r="G57">
-        <v>-16.08063904293761</v>
+        <v>-16.78287295620373</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.1390048987360789</v>
       </c>
       <c r="E58">
-        <v>-28.09378082481102</v>
+        <v>-30.64004892560691</v>
       </c>
       <c r="F58">
-        <v>-3.29962773914475</v>
+        <v>-3.075171650947391</v>
       </c>
       <c r="G58">
-        <v>-16.3729581498362</v>
+        <v>-16.66132994719878</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.1298183262479089</v>
       </c>
       <c r="E59">
-        <v>-28.322251395446</v>
+        <v>-30.85012709905974</v>
       </c>
       <c r="F59">
-        <v>-3.544520479536577</v>
+        <v>-3.588303838611544</v>
       </c>
       <c r="G59">
-        <v>-16.32242897843154</v>
+        <v>-16.70404488945963</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.1228438126105403</v>
       </c>
       <c r="E60">
-        <v>-27.71864203801561</v>
+        <v>-29.53776174621484</v>
       </c>
       <c r="F60">
-        <v>-3.308321455037131</v>
+        <v>-3.384188311989927</v>
       </c>
       <c r="G60">
-        <v>-16.14583035288066</v>
+        <v>-17.21528381758282</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.1252058162341764</v>
       </c>
       <c r="E61">
-        <v>-27.61432411077491</v>
+        <v>-30.6727535648903</v>
       </c>
       <c r="F61">
-        <v>-3.6407237562281</v>
+        <v>-3.887270746323317</v>
       </c>
       <c r="G61">
-        <v>-16.7433768922927</v>
+        <v>-17.37096629630301</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.142154850743156</v>
       </c>
       <c r="E62">
-        <v>-27.23270054920052</v>
+        <v>-29.96678258099052</v>
       </c>
       <c r="F62">
-        <v>-3.741690145485721</v>
+        <v>-3.442031550992611</v>
       </c>
       <c r="G62">
-        <v>-16.67449748931683</v>
+        <v>-17.35158083932981</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.1779131208974815</v>
       </c>
       <c r="E63">
-        <v>-27.46856158941602</v>
+        <v>-28.95997827605019</v>
       </c>
       <c r="F63">
-        <v>-3.6669697490184</v>
+        <v>-3.536065333456202</v>
       </c>
       <c r="G63">
-        <v>-16.57691396013895</v>
+        <v>-17.85316969484667</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.2333627913938415</v>
       </c>
       <c r="E64">
-        <v>-26.59350191454384</v>
+        <v>-30.05560180593996</v>
       </c>
       <c r="F64">
-        <v>-3.531051225567057</v>
+        <v>-3.514275128925561</v>
       </c>
       <c r="G64">
-        <v>-17.12260899585786</v>
+        <v>-18.00014873338043</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.3090067883107077</v>
       </c>
       <c r="E65">
-        <v>-26.56555217296849</v>
+        <v>-28.49368583595438</v>
       </c>
       <c r="F65">
-        <v>-3.702343522220147</v>
+        <v>-3.658694358664432</v>
       </c>
       <c r="G65">
-        <v>-16.78395904053991</v>
+        <v>-17.74244979515554</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.4020368418473856</v>
       </c>
       <c r="E66">
-        <v>-26.86079962132059</v>
+        <v>-28.82521541805593</v>
       </c>
       <c r="F66">
-        <v>-4.012339313532792</v>
+        <v>-3.665458806875693</v>
       </c>
       <c r="G66">
-        <v>-17.21378265871937</v>
+        <v>-18.31341187749296</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.5083565538023798</v>
       </c>
       <c r="E67">
-        <v>-26.28177082080382</v>
+        <v>-28.57166615836647</v>
       </c>
       <c r="F67">
-        <v>-4.055044966616718</v>
+        <v>-3.936295185955797</v>
       </c>
       <c r="G67">
-        <v>-17.15990992254563</v>
+        <v>-18.04900612240057</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.6208159996490819</v>
       </c>
       <c r="E68">
-        <v>-26.20526678091824</v>
+        <v>-28.74180092683464</v>
       </c>
       <c r="F68">
-        <v>-4.015357884348593</v>
+        <v>-3.799107603643366</v>
       </c>
       <c r="G68">
-        <v>-17.22962439640837</v>
+        <v>-18.1006952056265</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.7324431775380428</v>
       </c>
       <c r="E69">
-        <v>-25.51663532399384</v>
+        <v>-28.71521878440961</v>
       </c>
       <c r="F69">
-        <v>-4.137307648286528</v>
+        <v>-3.723780842237195</v>
       </c>
       <c r="G69">
-        <v>-17.1000243478642</v>
+        <v>-17.42223866439089</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.8351076256760309</v>
       </c>
       <c r="E70">
-        <v>-25.80575121853954</v>
+        <v>-28.46221747007508</v>
       </c>
       <c r="F70">
-        <v>-4.09644179920422</v>
+        <v>-3.997147883732852</v>
       </c>
       <c r="G70">
-        <v>-17.0691660997084</v>
+        <v>-16.90031771948094</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.9225008892990322</v>
       </c>
       <c r="E71">
-        <v>-25.79686182406248</v>
+        <v>-27.62845747815285</v>
       </c>
       <c r="F71">
-        <v>-4.326164647348579</v>
+        <v>-4.239558007018488</v>
       </c>
       <c r="G71">
-        <v>-17.13565513277821</v>
+        <v>-18.05999329279237</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.9890032381518443</v>
       </c>
       <c r="E72">
-        <v>-25.75809355808282</v>
+        <v>-27.99273245580386</v>
       </c>
       <c r="F72">
-        <v>-4.271081528532023</v>
+        <v>-4.48698223819327</v>
       </c>
       <c r="G72">
-        <v>-16.84151494791413</v>
+        <v>-17.79817149967803</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.031596734412632</v>
       </c>
       <c r="E73">
-        <v>-25.4712147296969</v>
+        <v>-28.6598898889839</v>
       </c>
       <c r="F73">
-        <v>-4.623506298216059</v>
+        <v>-4.363693004165007</v>
       </c>
       <c r="G73">
-        <v>-16.65146659519109</v>
+        <v>-17.03705934674924</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.048080827878684</v>
       </c>
       <c r="E74">
-        <v>-25.8289279485108</v>
+        <v>-27.95013310081371</v>
       </c>
       <c r="F74">
-        <v>-4.491431399513705</v>
+        <v>-4.670705844460172</v>
       </c>
       <c r="G74">
-        <v>-16.68884134936395</v>
+        <v>-17.59090329621103</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.038487318141789</v>
       </c>
       <c r="E75">
-        <v>-26.72547523254937</v>
+        <v>-28.28764026860538</v>
       </c>
       <c r="F75">
-        <v>-4.438509491251054</v>
+        <v>-4.337659073429825</v>
       </c>
       <c r="G75">
-        <v>-16.67397741569966</v>
+        <v>-17.42420575671578</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.003162947388597</v>
       </c>
       <c r="E76">
-        <v>-26.38031947215875</v>
+        <v>-28.04930215310768</v>
       </c>
       <c r="F76">
-        <v>-4.47670302709193</v>
+        <v>-4.775385804784542</v>
       </c>
       <c r="G76">
-        <v>-16.15528355219342</v>
+        <v>-17.64771600690204</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.944273393870332</v>
       </c>
       <c r="E77">
-        <v>-26.18412786425044</v>
+        <v>-29.64611454379637</v>
       </c>
       <c r="F77">
-        <v>-4.51956358488018</v>
+        <v>-4.67490401045756</v>
       </c>
       <c r="G77">
-        <v>-15.96612769173455</v>
+        <v>-17.00806975427155</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.865270166396051</v>
       </c>
       <c r="E78">
-        <v>-26.82635604801825</v>
+        <v>-28.76971444061792</v>
       </c>
       <c r="F78">
-        <v>-4.601870998389741</v>
+        <v>-4.748990705861739</v>
       </c>
       <c r="G78">
-        <v>-15.76493631059564</v>
+        <v>-16.43885000058219</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.7735515691120881</v>
       </c>
       <c r="E79">
-        <v>-26.73187849479622</v>
+        <v>-30.12073031911828</v>
       </c>
       <c r="F79">
-        <v>-4.592293414478573</v>
+        <v>-4.785969855090112</v>
       </c>
       <c r="G79">
-        <v>-15.56968722170088</v>
+        <v>-16.22709636724343</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.6779295930642543</v>
       </c>
       <c r="E80">
-        <v>-27.59753705762848</v>
+        <v>-30.45802464863159</v>
       </c>
       <c r="F80">
-        <v>-4.65475645848667</v>
+        <v>-4.916897464939588</v>
       </c>
       <c r="G80">
-        <v>-15.34183919661304</v>
+        <v>-16.76084611587518</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.5889103309915853</v>
       </c>
       <c r="E81">
-        <v>-27.90778281189397</v>
+        <v>-30.1930047642807</v>
       </c>
       <c r="F81">
-        <v>-4.888971543056411</v>
+        <v>-4.796036175768932</v>
       </c>
       <c r="G81">
-        <v>-15.68371295211315</v>
+        <v>-16.33317497903872</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.5142154700539388</v>
       </c>
       <c r="E82">
-        <v>-28.06434121528715</v>
+        <v>-29.70906938945101</v>
       </c>
       <c r="F82">
-        <v>-4.788893163654591</v>
+        <v>-4.828528887143742</v>
       </c>
       <c r="G82">
-        <v>-14.93961393297007</v>
+        <v>-16.29773122375359</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.4619025160726102</v>
       </c>
       <c r="E83">
-        <v>-29.0471242298538</v>
+        <v>-30.37180703199956</v>
       </c>
       <c r="F83">
-        <v>-4.867075307498212</v>
+        <v>-4.795457975321777</v>
       </c>
       <c r="G83">
-        <v>-14.7595437750093</v>
+        <v>-15.77755588871326</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.4363997234921549</v>
       </c>
       <c r="E84">
-        <v>-29.44415366000229</v>
+        <v>-31.31101254119039</v>
       </c>
       <c r="F84">
-        <v>-4.963339055010139</v>
+        <v>-4.656539933504898</v>
       </c>
       <c r="G84">
-        <v>-14.55321564151908</v>
+        <v>-15.90083794514472</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4434900565362239</v>
       </c>
       <c r="E85">
-        <v>-30.19759210845047</v>
+        <v>-32.08198524099627</v>
       </c>
       <c r="F85">
-        <v>-4.888391685874451</v>
+        <v>-5.420446270120754</v>
       </c>
       <c r="G85">
-        <v>-14.36713264505063</v>
+        <v>-15.4729125136374</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4839102808459425</v>
       </c>
       <c r="E86">
-        <v>-31.16753237073136</v>
+        <v>-33.61957877708665</v>
       </c>
       <c r="F86">
-        <v>-5.038174594546449</v>
+        <v>-5.151515964434491</v>
       </c>
       <c r="G86">
-        <v>-14.01878996124608</v>
+        <v>-15.60137233768966</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.5603739407637132</v>
       </c>
       <c r="E87">
-        <v>-31.56765474862709</v>
+        <v>-34.62495887695157</v>
       </c>
       <c r="F87">
-        <v>-5.05594638880611</v>
+        <v>-5.176603899595677</v>
       </c>
       <c r="G87">
-        <v>-13.94184695628788</v>
+        <v>-15.19014832391991</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6694779567118304</v>
       </c>
       <c r="E88">
-        <v>-33.13848275545977</v>
+        <v>-35.28498622780653</v>
       </c>
       <c r="F88">
-        <v>-5.231116273271705</v>
+        <v>-4.803224748090425</v>
       </c>
       <c r="G88">
-        <v>-14.02651887862936</v>
+        <v>-15.26679601893776</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8109979376961501</v>
       </c>
       <c r="E89">
-        <v>-34.10900039817663</v>
+        <v>-37.14590375109656</v>
       </c>
       <c r="F89">
-        <v>-5.168740207840901</v>
+        <v>-5.437253016356153</v>
       </c>
       <c r="G89">
-        <v>-14.23199225390334</v>
+        <v>-14.72934997421929</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9779679838517352</v>
       </c>
       <c r="E90">
-        <v>-34.94860891427977</v>
+        <v>-37.27440372953821</v>
       </c>
       <c r="F90">
-        <v>-5.278671189131619</v>
+        <v>-5.382110255086595</v>
       </c>
       <c r="G90">
-        <v>-14.12568395659889</v>
+        <v>-14.92789340955973</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.169000708251084</v>
       </c>
       <c r="E91">
-        <v>-35.88678645987086</v>
+        <v>-38.75255425156691</v>
       </c>
       <c r="F91">
-        <v>-5.292201742288945</v>
+        <v>-5.640682654768253</v>
       </c>
       <c r="G91">
-        <v>-13.55945667697176</v>
+        <v>-15.19413172689308</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.377177907421119</v>
       </c>
       <c r="E92">
-        <v>-37.5456208305686</v>
+        <v>-39.04300151747088</v>
       </c>
       <c r="F92">
-        <v>-5.590480276688992</v>
+        <v>-5.833092521620911</v>
       </c>
       <c r="G92">
-        <v>-13.83520233377359</v>
+        <v>-15.86816682207733</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.603299344226758</v>
       </c>
       <c r="E93">
-        <v>-38.83857487957962</v>
+        <v>-40.44330757130773</v>
       </c>
       <c r="F93">
-        <v>-5.287935650164528</v>
+        <v>-5.816384351106445</v>
       </c>
       <c r="G93">
-        <v>-13.95016157171952</v>
+        <v>-15.72408182095899</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.842044454826991</v>
       </c>
       <c r="E94">
-        <v>-40.48502840234039</v>
+        <v>-41.43250290506923</v>
       </c>
       <c r="F94">
-        <v>-5.565672329709952</v>
+        <v>-5.779160005126843</v>
       </c>
       <c r="G94">
-        <v>-14.08420603486595</v>
+        <v>-15.40592801611212</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.094874920651768</v>
       </c>
       <c r="E95">
-        <v>-42.04925389406989</v>
+        <v>-43.86203147442138</v>
       </c>
       <c r="F95">
-        <v>-5.462162852525737</v>
+        <v>-5.710896732564344</v>
       </c>
       <c r="G95">
-        <v>-14.3641089993836</v>
+        <v>-15.67963275310398</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.357200170016546</v>
       </c>
       <c r="E96">
-        <v>-43.62772822926451</v>
+        <v>-45.20832868300575</v>
       </c>
       <c r="F96">
-        <v>-5.767209148606655</v>
+        <v>-6.153094991159374</v>
       </c>
       <c r="G96">
-        <v>-14.69865414653069</v>
+        <v>-15.73285908863051</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.627674029029289</v>
       </c>
       <c r="E97">
-        <v>-44.81547903436633</v>
+        <v>-46.21860406327296</v>
       </c>
       <c r="F97">
-        <v>-5.753274352156762</v>
+        <v>-5.797887735369335</v>
       </c>
       <c r="G97">
-        <v>-14.74865996309663</v>
+        <v>-16.04551520675454</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.900081525480244</v>
       </c>
       <c r="E98">
-        <v>-46.87381538202076</v>
+        <v>-48.61869755157525</v>
       </c>
       <c r="F98">
-        <v>-5.654632361831396</v>
+        <v>-5.68270821821448</v>
       </c>
       <c r="G98">
-        <v>-14.98599235910204</v>
+        <v>-16.04379584665739</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.165092936686612</v>
       </c>
       <c r="E99">
-        <v>-48.61947078851206</v>
+        <v>-50.25617790308983</v>
       </c>
       <c r="F99">
-        <v>-5.780555804200561</v>
+        <v>-6.336167500647676</v>
       </c>
       <c r="G99">
-        <v>-15.06758485500997</v>
+        <v>-16.79020320516753</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.413258747437013</v>
       </c>
       <c r="E100">
-        <v>-50.68051063514906</v>
+        <v>-51.34744051251021</v>
       </c>
       <c r="F100">
-        <v>-5.807234204775122</v>
+        <v>-6.21201013758128</v>
       </c>
       <c r="G100">
-        <v>-15.58719746055286</v>
+        <v>-16.61338637838296</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.622972605263381</v>
       </c>
       <c r="E101">
-        <v>-51.74260760772305</v>
+        <v>-52.43145982775533</v>
       </c>
       <c r="F101">
-        <v>-5.763286828954399</v>
+        <v>-6.40786477027848</v>
       </c>
       <c r="G101">
-        <v>-15.72566665097221</v>
+        <v>-17.42343631026009</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.790703037945256</v>
       </c>
       <c r="E102">
-        <v>-53.73317081337868</v>
+        <v>-54.13418643277242</v>
       </c>
       <c r="F102">
-        <v>-6.082819614175475</v>
+        <v>-5.973358317202146</v>
       </c>
       <c r="G102">
-        <v>-15.56174502491625</v>
+        <v>-16.87696526564237</v>
       </c>
     </row>
   </sheetData>
